--- a/_tooling/CABRU_testi_IT_da_correggere.xlsx
+++ b/_tooling/CABRU_testi_IT_da_correggere.xlsx
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Sui kit di estrazione la referenza giusta dipende quasi sempre da due sole variabili: la matrice di partenza e ciò che si deve fare a valle. CABRU parte da lì — tipo di campione, volume, applicazione successiva — e indica il kit coerente. CABRU rappresenta A&amp;A Biotechnology in Italia offrendo informazioni tecniche, preventivi competitivi e gestione dell'ordine fino alla consegna. CABRU distribuisce A&amp;A Biotechnology in Italia in regime non esclusivo. È sufficiente contattare CABRU a info@cabru.it. → Richiedi informazioni e preventivo</t>
+          <t>Sui kit di estrazione la referenza giusta dipende quasi sempre da due sole variabili: la matrice di partenza e ciò che si deve fare a valle. CABRU parte da lì — tipo di campione, volume, applicazione successiva — e indica il kit coerente. CABRU rappresenta A&amp;A Biotechnology in Italia offrendo informazioni tecniche, preventivi e gestione dell'ordine fino alla consegna. CABRU distribuisce A&amp;A Biotechnology in Italia in regime non esclusivo. È sufficiente contattare CABRU a info@cabru.it. → Richiedi informazioni e preventivo</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr"/>
